--- a/network_excel_transformer/output/2G3G4G_Cell Info_SITES_2G.xlsx
+++ b/network_excel_transformer/output/2G3G4G_Cell Info_SITES_2G.xlsx
@@ -469,12 +469,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3G_GagnoaAnader</t>
+          <t>2G_GagnoaAnader</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -492,12 +492,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>3G_BINHOUNIENSOUSPREFECTURE</t>
+          <t>2G_BINHOUNIENSOUSPREFECTURE</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>3G_ROXGOLDNEW</t>
+          <t>2G_ROXGOLDNEW</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -538,12 +538,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>3G_TOULEUPLEUMAIRIE</t>
+          <t>2G_TOULEUPLEUMAIRIE</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -561,12 +561,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3G_ZAGNEGLAZA</t>
+          <t>2G_ZAGNEGLAZA</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -584,12 +584,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3G_AdjameMotagri</t>
+          <t>2G_AdjameMotagri</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3G_AdjameCampGalieni</t>
+          <t>2G_AdjameCampGalieni</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -630,12 +630,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3G_AboboVesos</t>
+          <t>2G_AboboVesos</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -653,12 +653,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>3G_AnyamaMarche</t>
+          <t>2G_AnyamaMarche</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>3G_AssiniePoton</t>
+          <t>2G_AssiniePoton</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -699,12 +699,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3G_AttecoubePoleBoulevardDeLaPaix</t>
+          <t>2G_AttecoubePoleBoulevardDeLaPaix</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>3G_BonouaDingui</t>
+          <t>2G_BonouaDingui</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>3G_CocodyKanate</t>
+          <t>2G_CocodyKanate</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>3G_CocodyManhattan</t>
+          <t>2G_CocodyManhattan</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -791,12 +791,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>3G_CocodyPhamacieSainteMarie</t>
+          <t>2G_CocodyPhamacieSainteMarie</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>3G_MarcoryResidentielLagune</t>
+          <t>2G_MarcoryResidentielLagune</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>3G_Niakara2</t>
+          <t>2G_Niakara2</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>3G_PortBouetJeanFolly2</t>
+          <t>2G_PortBouetJeanFolly2</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3G_YopougonAnaneraieStationPETROCI</t>
+          <t>2G_YopougonAnaneraieStationPETROCI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>3G_YopougonAssomption</t>
+          <t>2G_YopougonAssomption</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>3G_YopougonEgliseStAndre</t>
+          <t>2G_YopougonEgliseStAndre</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>3G_YopougonNgoh</t>
+          <t>2G_YopougonNgoh</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -975,12 +975,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>3G_PortBouetSirene2</t>
+          <t>2G_PortBouetSirene2</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>3G_BingerPalaisJustice</t>
+          <t>2G_BingerPalaisJustice</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>3G_TreichvilleBelleVille</t>
+          <t>2G_TreichvilleBelleVille</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>3G_SanPedroCathedrale2</t>
+          <t>2G_SanPedroCathedrale2</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>3G_SanpedroBardoNew</t>
+          <t>2G_SanpedroBardoNew</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>3G_ManCNPS</t>
+          <t>2G_ManCNPS</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>3G_AllokoiUsineDangoteCement</t>
+          <t>2G_AllokoiUsineDangoteCement</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1136,12 +1136,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>3G_PAILLOTE</t>
+          <t>2G_PAILLOTE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>3G_CocodyRivieraGolf4</t>
+          <t>2G_CocodyRivieraGolf4</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>3G_AllokoiZIParadisCosmetique</t>
+          <t>2G_AllokoiZIParadisCosmetique</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1205,12 +1205,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>3G_ManPouponnière</t>
+          <t>2G_ManPouponnière</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>3G_DaloaOrlyCentre</t>
+          <t>2G_DaloaOrlyCentre</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>3G_AdjameDallas</t>
+          <t>2G_AdjameDallas</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>3G_DokuiBad</t>
+          <t>2G_DokuiBad</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>WCDMA_Site</t>
+          <t>GSM_Site</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>3G_Modeste3</t>
+          <t>2G_Modeste3</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
